--- a/reports/bui_style/bui_style_tables.xlsx
+++ b/reports/bui_style/bui_style_tables.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shear" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biaxial" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combined" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bui 2011 Table 1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bui 2011 Table 2" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1113,4 +1115,493 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>7x7</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>9x9</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>11x11</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>13x13</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>15x15</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>17x17</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Exact [1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CCCC</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>951.2794181153163</v>
+      </c>
+      <c r="C2" t="n">
+        <v>536.2115320449841</v>
+      </c>
+      <c r="D2" t="n">
+        <v>346.6046375538991</v>
+      </c>
+      <c r="E2" t="n">
+        <v>244.1825915163592</v>
+      </c>
+      <c r="F2" t="n">
+        <v>182.5804351759248</v>
+      </c>
+      <c r="G2" t="n">
+        <v>142.6400510789432</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10.07</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CSCS</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>684.8615926993177</v>
+      </c>
+      <c r="C3" t="n">
+        <v>397.6406069329877</v>
+      </c>
+      <c r="D3" t="n">
+        <v>260.9280534870946</v>
+      </c>
+      <c r="E3" t="n">
+        <v>185.420780892245</v>
+      </c>
+      <c r="F3" t="n">
+        <v>139.3922822436636</v>
+      </c>
+      <c r="G3" t="n">
+        <v>109.2849878949931</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SCSC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>620.2962367510775</v>
+      </c>
+      <c r="C4" t="n">
+        <v>350.1689512147823</v>
+      </c>
+      <c r="D4" t="n">
+        <v>226.9719081314815</v>
+      </c>
+      <c r="E4" t="n">
+        <v>160.293808240033</v>
+      </c>
+      <c r="F4" t="n">
+        <v>120.0985804887105</v>
+      </c>
+      <c r="G4" t="n">
+        <v>93.9835529520952</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SSSS</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>377.7067633536244</v>
+      </c>
+      <c r="C5" t="n">
+        <v>225.6285094120467</v>
+      </c>
+      <c r="D5" t="n">
+        <v>150.5352082111933</v>
+      </c>
+      <c r="E5" t="n">
+        <v>108.1272645518625</v>
+      </c>
+      <c r="F5" t="n">
+        <v>81.87562298091133</v>
+      </c>
+      <c r="G5" t="n">
+        <v>64.50654367594666</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FSCS</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>178.7334850281789</v>
+      </c>
+      <c r="C6" t="n">
+        <v>102.9856894060247</v>
+      </c>
+      <c r="D6" t="n">
+        <v>67.25986591777256</v>
+      </c>
+      <c r="E6" t="n">
+        <v>47.62944981695416</v>
+      </c>
+      <c r="F6" t="n">
+        <v>35.70024643089198</v>
+      </c>
+      <c r="G6" t="n">
+        <v>27.9127649257578</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FSSS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>141.8823385982459</v>
+      </c>
+      <c r="C7" t="n">
+        <v>82.35350763217889</v>
+      </c>
+      <c r="D7" t="n">
+        <v>54.03823417278545</v>
+      </c>
+      <c r="E7" t="n">
+        <v>38.39289730380561</v>
+      </c>
+      <c r="F7" t="n">
+        <v>28.84737634274314</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22.59718541740465</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Exact [1]</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FEM [45]</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BEM [45]</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>DRM [45]</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>SFSM [34]</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SFSM [33]</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>RPIM [70]</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>DQEM [42]</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>DSC [58]</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CCCC</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10.392</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10.387</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10.142</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10.109</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10.308</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10.052</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="K2" t="n">
+        <v>244.1825915163592</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CSCS</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7.796</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7.757</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7.683</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7.712</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7.681</v>
+      </c>
+      <c r="K3" t="n">
+        <v>185.420780892245</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SCSC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="C4" t="n">
+        <v>6.882</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.972</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6.781</v>
+      </c>
+      <c r="K4" t="n">
+        <v>160.293808240033</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SSSS</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4.011</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.041</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.017</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.9977</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.011</v>
+      </c>
+      <c r="K5" t="n">
+        <v>108.1272645518625</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FSCS</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.718</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.712</v>
+      </c>
+      <c r="K6" t="n">
+        <v>47.62944981695416</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FSSS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.422</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.428</v>
+      </c>
+      <c r="K7" t="n">
+        <v>38.39289730380561</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>